--- a/data/processed/harmonization/Biology__Microbial_biomass_carbon/10.15485_1577267/10.15485_1577267_soil_Biology__Microbial_biomass_carbon.xlsx
+++ b/data/processed/harmonization/Biology__Microbial_biomass_carbon/10.15485_1577267/10.15485_1577267_soil_Biology__Microbial_biomass_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>East_River:1</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2016-09-12:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>East_River:2</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2016-09-12:2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>East_River:3</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2016-09-12:3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>East_River:4</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2016-09-12:4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>East_River:5</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2016-09-12:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>East_River:6</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2016-09-12:6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>East_River:7</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2016-09-12:7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>East_River:8</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2016-09-12:8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>East_River:9</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2016-09-12:9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>East_River:10</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2016-09-12:10</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>East_River:11</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2016-09-12:11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>East_River:12</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2016-09-12:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>East_River:13</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2016-09-12:13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>East_River:14</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2016-09-12:14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>East_River:15</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2016-09-12:15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>East_River:16</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2016-09-12:16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>East_River:17</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2016-09-12:17</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>East_River:18</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2016-09-12:18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>East_River:19</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2016-09-12:19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>East_River:20</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2016-09-12:20</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>East_River:21</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2016-09-12:21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>East_River:22</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2016-09-12:22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>East_River:23</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2016-09-12:23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>East_River:24</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2016-09-12:24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>East_River:25</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2016-09-12:25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>East_River:26</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2016-09-12:26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>East_River:27</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2016-09-12:27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>East_River:28</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2016-09-12:28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>East_River:29</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2016-09-12:29</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>East_River:31</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2016-09-12:31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>East_River:32</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2016-09-12:32</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>East_River:33</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2016-09-12:33</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>East_River:34</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2016-09-12:34</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>East_River:35</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2016-09-12:35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>East_River:36</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2016-09-12:36</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>East_River:37</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Upslope:1:0-5:2016-09-12:37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>East_River:38</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Upslope:1:5-15:2016-09-12:38</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>East_River:39</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Upslope:1:15 cm +:2016-09-12:39</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>East_River:41</t>
+          <t>F2:East_River:Pumphouse_Floodplain:Upslope:2:5-15:2016-09-12:41</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>East_River:43</t>
+          <t>F3:East_River:Pumphouse_Floodplain:Upslope:3:0-5:2016-09-12:43</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>East_River:45</t>
+          <t>F3:East_River:Pumphouse_Floodplain:Upslope:3:15 cm +:2016-09-12:45</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:67</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2016-10-20:67</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:68</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2016-10-20:68</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:69</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2016-10-20:69</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:70</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:1:0-5:2016-10-20:70</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:71</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:1:5-15:2016-10-20:71</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:72</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:1:15 cm +:2016-10-20:72</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:73</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2016-10-20:73</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:74</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2016-10-20:74</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:75</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2016-10-20:75</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:76</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:1:0-5:2016-10-20:76</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:77</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:1:5-15:2016-10-20:77</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:78</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:1:15 cm +:2016-10-20:78</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:79</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2016-10-20:79</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:80</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2016-10-20:80</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:81</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2016-10-20:81</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:82</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:1:0-5:2016-10-20:82</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:83</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:1:5-15:2016-10-20:83</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:84</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:1:15 cm +:2016-10-20:84</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:85</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Upslope:1:0-5:2016-10-20:85</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:86</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Upslope:1:5-15:2016-10-20:86</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:87</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Upslope:1:15 cm +:2016-10-20:87</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:88</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Downslope:1:0-5:2016-10-20:88</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:89</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Downslope:1:5-15:2016-10-20:89</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:90</t>
+          <t>A1:Washington_Gulch:Upper_Subalpine:Downslope:1:15 cm +:2016-10-20:90</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:91</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Upslope:1:0-5:2016-10-20:91</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:92</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Upslope:1:5-15:2016-10-20:92</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:93</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Upslope:1:15 cm +:2016-10-20:93</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:94</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Downslope:1:0-5:2016-10-20:94</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:95</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Downslope:1:5-15:2016-10-20:95</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:96</t>
+          <t>B1:Washington_Gulch:Upper_Subalpine:Downslope:1:15 cm +:2016-10-20:96</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:97</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Upslope:1:0-5:2016-10-20:97</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:98</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Upslope:1:5-15:2016-10-20:98</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:99</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Upslope:1:15 cm +:2016-10-20:99</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:100</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Downslope:1:0-5:2016-10-20:100</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:101</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Downslope:1:5-15:2016-10-20:101</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:102</t>
+          <t>C1:Washington_Gulch:Upper_Subalpine:Downslope:1:15 cm +:2016-10-20:102</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:103</t>
+          <t>A1:Washington_Gulch:Alpine:Upslope:1:0-5:2016-10-20:103</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:104</t>
+          <t>A1:Washington_Gulch:Alpine:Upslope:1:5-15:2016-10-20:104</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:105</t>
+          <t>A1:Washington_Gulch:Alpine:Upslope:1:15 cm +:2016-10-20:105</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:106</t>
+          <t>A1:Washington_Gulch:Alpine:Downslope:1:0-5:2016-10-20:106</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:107</t>
+          <t>A1:Washington_Gulch:Alpine:Downslope:1:5-15:2016-10-20:107</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:108</t>
+          <t>A1:Washington_Gulch:Alpine:Downslope:1:15 cm +:2016-10-20:108</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>East_River:112</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:1:0-5:2017-03-07:112</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>East_River:113</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:1:5-15:2017-03-07:113</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>East_River:114</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:1:15 cm +:2017-03-07:114</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>East_River:115</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:2:0-5:2017-03-07:115</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>East_River:116</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:2:5-15:2017-03-07:116</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>East_River:117</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow_Pit_A1:2:15 cm +:2017-03-07:117</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>East_River:118</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:1:0-5:2017-03-07:118</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>East_River:119</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:1:5-15:2017-03-07:119</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>East_River:120</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:1:15 cm +:2017-03-07:120</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>East_River:121</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:2:0-5:2017-03-07:121</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>East_River:122</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:2:5-15:2017-03-07:122</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>East_River:123</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow_Pit_B1:2:15 cm +:2017-03-07:123</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>East_River:125</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:1:5-15:2017-03-07:125</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>East_River:126</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:1:15 cm +:2017-03-07:126</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>East_River:127</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:2:0-5:2017-03-07:127</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>East_River:128</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:2:5-15:2017-03-07:128</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>East_River:129</t>
+          <t>F1:East_River:Pumphouse_Floodplain:Snow_Pit_F1:2:15 cm +:2017-03-07:129</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>East_River:133</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:1:0-5:2017-05-09:133</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>East_River:134</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:2:5-15:2017-05-09:134</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>East_River:135</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:3:15 cm +:2017-05-09:135</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>East_River:136</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:1:0-5:2017-05-09:136</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>East_River:137</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:2:5-15:2017-05-09:137</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>East_River:138</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:3:15 cm +:2017-05-09:138</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>East_River:139</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:1:0-5:2017-05-09:139</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>East_River:140</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:2:5-15:2017-05-09:140</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>East_River:141</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Snow PitA1:3:15 cm +:2017-05-09:141</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>East_River:142</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:1:0-5:2017-05-09:142</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>East_River:143</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:2:5-15:2017-05-09:143</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>East_River:144</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:3:15 cm +:2017-05-09:144</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>East_River:145</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:1:0-5:2017-05-09:145</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>East_River:146</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:2:5-15:2017-05-09:146</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>East_River:147</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:3:15 cm +:2017-05-09:147</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>East_River:148</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:1:0-5:2017-05-09:148</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>East_River:149</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:2:5-15:2017-05-09:149</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>East_River:150</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Snow PitB1:3:15 cm +:2017-05-09:150</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>East_River:151</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:1:0-5:2017-05-09:151</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>East_River:152</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:2:5-15:2017-05-09:152</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6858,12 +6858,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>East_River:153</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:3:15 cm +:2017-05-09:153</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>East_River:154</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:1:0-5:2017-05-09:154</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>East_River:155</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:2:5-15:2017-05-09:155</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>East_River:156</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:3:15 cm +:2017-05-09:156</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>East_River:158</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:2:5-15:2017-05-09:158</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>East_River:159</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Snow PitC1:3:15 cm +:2017-05-09:159</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>East_River:160</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-05-09:160</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>East_River:161</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-05-09:161</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>East_River:162</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-05-09:162</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>East_River:163</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-05-09:163</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>East_River:164</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-05-09:164</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>East_River:165</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-05-09:165</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>East_River:166</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-05-09:166</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>East_River:167</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-05-09:167</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>East_River:168</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-05-09:168</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>East_River:172</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-06-09:172</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>East_River:174</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-06-09:174</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>East_River:175</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2017-06-09:175</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>East_River:176</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2017-06-09:176</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>East_River:177</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2017-06-09:177</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>East_River:178</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2017-06-09:178</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>East_River:179</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2017-06-09:179</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>East_River:180</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2017-06-09:180</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>East_River:181</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-06-09:181</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>East_River:182</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2017-06-09:182</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>East_River:184</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-06-09:184</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>East_River:186</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-06-09:186</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>East_River:187</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2017-06-09:187</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>East_River:188</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:5-15:2017-06-09:188</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>East_River:189</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2017-06-09:189</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>East_River:190</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2017-06-09:190</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>East_River:191</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2017-06-09:191</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>East_River:192</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2017-06-09:192</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>East_River:193</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-06-09:193</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8658,12 +8658,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>East_River:194</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:5-15:2017-06-09:194</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>East_River:196</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-06-09:196</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>East_River:197</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:5-15:2017-06-09:197</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>East_River:198</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-06-09:198</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>East_River:201</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2017-06-09:201</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>East_River:202</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2017-06-09:202</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>East_River:203</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:5-15:2017-06-09:203</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>East_River:204</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2017-06-09:204</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>East_River:205</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-06-09:205</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>East_River:207</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-06-09:207</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>East_River:208</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-06-09:208</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>East_River:209</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:5-15:2017-06-09:209</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>East_River:210</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:15 cm +:2017-06-09:210</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9362,12 +9362,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>East_River:212</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:5-15:2017-06-09:212</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>East_River:213</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:15 cm +:2017-06-09:213</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>East_River:215</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:5-15:2017-06-09:215</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>East_River:216</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-06-09:216</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:235</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-06-09:235</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:237</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-06-09:237</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:241</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-06-09:241</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:242</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:5-15:2017-06-09:242</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:243</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-06-09:243</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:247</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-06-09:247</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>East_River:256</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-07-24:256</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>East_River:257</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-07-24:257</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9986,12 +9986,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>East_River:258</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-07-24:258</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>East_River:259</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-07-24:259</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>East_River:260</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-07-24:260</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>East_River:261</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-07-24:261</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10194,12 +10194,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>East_River:262</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-07-24:262</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>East_River:263</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-07-24:263</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>East_River:264</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-07-24:264</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>East_River:265</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-07-24:265</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10402,12 +10402,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>East_River:266</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-07-24:266</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>East_River:267</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-07-24:267</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>East_River:268</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-07-24:268</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>East_River:269</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-07-24:269</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10610,12 +10610,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>East_River:270</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-07-24:270</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>East_River:271</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-07-24:271</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>East_River:272</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-07-24:272</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>East_River:273</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-07-24:273</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>East_River:274</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-07-24:274</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>East_River:275</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-07-24:275</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>East_River:278</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-07-24:278</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>East_River:283</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-07-24:283</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>East_River:284</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-07-24:284</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -11078,12 +11078,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>East_River:289</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:0-5:2017-07-24:289</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>East_River:293</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15-May:2017-07-24:293</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>East_River:294</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-07-24:294</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:298</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-08-01:298</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:299</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:15-May:2017-08-01:299</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11338,12 +11338,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:300</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-08-01:300</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:301</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:2:0-5:2017-08-01:301</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11442,12 +11442,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:302</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:2:15-May:2017-08-01:302</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:303</t>
+          <t>A1:Washington_Gulch:Lower_Subalpine:Downslope:2:15 cm +:2017-08-01:303</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:304</t>
+          <t>A2:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-08-01:304</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:305</t>
+          <t>A2:Washington_Gulch:Lower_Subalpine:Upslope:1:15-May:2017-08-01:305</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:306</t>
+          <t>A2:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-08-01:306</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:307</t>
+          <t>A2:Washington_Gulch:Lower_Subalpine:Downslope:2:0-5:2017-08-01:307</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:308</t>
+          <t>A2:Washington_Gulch:Lower_Subalpine:Downslope:2:15-May:2017-08-01:308</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11806,12 +11806,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:309</t>
+          <t>A2:Washington_Gulch:Lower_Subalpine:Downslope:2:15 cm +:2017-08-01:309</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11858,12 +11858,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:310</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-08-01:310</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:311</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:15-May:2017-08-01:311</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:312</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-08-01:312</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -12014,12 +12014,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:313</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:2:0-5:2017-08-01:313</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:314</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:2:15-May:2017-08-01:314</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:315</t>
+          <t>B1:Washington_Gulch:Lower_Subalpine:Downslope:2:15 cm +:2017-08-01:315</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:316</t>
+          <t>B2:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-08-01:316</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:317</t>
+          <t>B2:Washington_Gulch:Lower_Subalpine:Upslope:1:15-May:2017-08-01:317</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:318</t>
+          <t>B2:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-08-01:318</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:319</t>
+          <t>B2:Washington_Gulch:Lower_Subalpine:Downslope:2:0-5:2017-08-01:319</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12378,12 +12378,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:320</t>
+          <t>B2:Washington_Gulch:Lower_Subalpine:Downslope:2:15-May:2017-08-01:320</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:321</t>
+          <t>B2:Washington_Gulch:Lower_Subalpine:Downslope:2:15 cm +:2017-08-01:321</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12482,12 +12482,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:322</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-08-01:322</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:323</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Upslope:1:15-May:2017-08-01:323</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12586,12 +12586,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:325</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:2:0-5:2017-08-01:325</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:326</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:2:15-May:2017-08-01:326</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:327</t>
+          <t>C1:Washington_Gulch:Lower_Subalpine:Downslope:2:15 cm +:2017-08-01:327</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12742,12 +12742,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:328</t>
+          <t>C2:Washington_Gulch:Lower_Subalpine:Upslope:1:0-5:2017-08-01:328</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:329</t>
+          <t>C2:Washington_Gulch:Lower_Subalpine:Upslope:1:15-May:2017-08-01:329</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:330</t>
+          <t>C2:Washington_Gulch:Lower_Subalpine:Upslope:1:15 cm +:2017-08-01:330</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:331</t>
+          <t>C2:Washington_Gulch:Lower_Subalpine:Downslope:2:0-5:2017-08-01:331</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:332</t>
+          <t>C2:Washington_Gulch:Lower_Subalpine:Downslope:2:15-May:2017-08-01:332</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Washington_Gulch:333</t>
+          <t>C2:Washington_Gulch:Lower_Subalpine:Downslope:2:15 cm +:2017-08-01:333</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -13054,12 +13054,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>East_River:352</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-09-15:352</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>East_River:353</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-09-15:353</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>East_River:354</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-09-15:354</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13210,12 +13210,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>East_River:356</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-09-15:356</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>East_River:358</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-09-15:358</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13318,12 +13318,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>East_River:359</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-09-15:359</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13370,12 +13370,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>East_River:360</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-09-15:360</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>East_River:362</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-09-15:362</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>East_River:363</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-09-15:363</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>East_River:364</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-09-15:364</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>East_River:365</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-09-15:365</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13630,12 +13630,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>East_River:366</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-09-15:366</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>East_River:367</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-09-15:367</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>East_River:368</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-09-15:368</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13794,12 +13794,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>East_River:369</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-09-15:369</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>East_River:370</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-09-15:370</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>East_River:371</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-09-15:371</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>East_River:372</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-09-15:372</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>East_River:373</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-09-15:373</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>East_River:374</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-09-15:374</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -14110,12 +14110,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>East_River:375</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-09-15:375</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -14162,12 +14162,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>East_River:376</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-09-15:376</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>East_River:377</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-09-15:377</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14266,12 +14266,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>East_River:378</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-09-15:378</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>East_River:379</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-09-15:379</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>East_River:380</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-09-15:380</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>East_River:381</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-09-15:381</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14486,12 +14486,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>East_River:382</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-09-15:382</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>East_River:383</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-09-15:383</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14590,12 +14590,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>East_River:384</t>
+          <t>C2:East_River:Pumphouse_Floodplain:Downslope:2:15 cm +:2017-09-15:384</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14642,12 +14642,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>East_River:388</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:0-5:2017-09-15:388</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14694,12 +14694,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>East_River:389</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:15-May:2017-09-15:389</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14746,12 +14746,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>East_River:390</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:15 cm +:2017-09-15:390</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>East_River:391</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:0-5:2017-09-15:391</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14850,12 +14850,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>East_River:392</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15-May:2017-09-15:392</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14902,12 +14902,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>East_River:393</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-09-15:393</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>East_River:397</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-10-27:397</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -15006,12 +15006,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>East_River:398</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-10-27:398</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>East_River:399</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-10-27:399</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>East_River:400</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:0-5:2017-10-27:400</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>East_River:401</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:15-May:2017-10-27:401</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>East_River:402</t>
+          <t>A1:East_River:Pumphouse_Hillslope:Downslope:1:15 cm +:2017-10-27:402</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>East_River:403</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:0-5:2017-10-27:403</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>East_River:404</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:15-May:2017-10-27:404</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -15370,12 +15370,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>East_River:405</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Upslope:2:15 cm +:2017-10-27:405</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -15422,12 +15422,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>East_River:406</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-10-27:406</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15474,12 +15474,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>East_River:407</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-10-27:407</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15526,12 +15526,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>East_River:408</t>
+          <t>A2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-10-27:408</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15578,12 +15578,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>East_River:409</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-10-27:409</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15630,12 +15630,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>East_River:410</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-10-27:410</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>East_River:411</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-10-27:411</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15734,12 +15734,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>East_River:412</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-10-27:412</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15786,12 +15786,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>East_River:413</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-10-27:413</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>East_River:414</t>
+          <t>B1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-10-27:414</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15890,12 +15890,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>East_River:415</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-10-27:415</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>East_River:416</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-10-27:416</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>East_River:417</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-10-27:417</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -16046,12 +16046,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>East_River:418</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-10-27:418</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -16098,12 +16098,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>East_River:419</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-10-27:419</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -16150,12 +16150,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>East_River:420</t>
+          <t>B2:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-10-27:420</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -16202,12 +16202,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>East_River:421</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-10-27:421</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>East_River:422</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-10-27:422</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -16306,12 +16306,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>East_River:423</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-10-27:423</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -16358,12 +16358,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>East_River:424</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-10-27:424</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -16410,12 +16410,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>East_River:425</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-10-27:425</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -16462,12 +16462,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>East_River:426</t>
+          <t>C1:East_River:Pumphouse_Hillslope:Downslope:2:15 cm +:2017-10-27:426</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16514,12 +16514,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>East_River:427</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:1:0-5:2017-10-27:427</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16566,12 +16566,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>East_River:428</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:1:15-May:2017-10-27:428</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>East_River:429</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Upslope:1:15 cm +:2017-10-27:429</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>East_River:430</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:0-5:2017-10-27:430</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16722,12 +16722,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>East_River:431</t>
+          <t>C2:East_River:Pumphouse_Hillslope:Downslope:2:15-May:2017-10-27:431</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16774,12 +16774,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>East_River:432</t>
+          <t>C2:East_River:Pumphouse_Floodplain:Downslope:2:15 cm +:2017-10-27:432</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16826,12 +16826,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>East_River:433</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:0-5:2017-10-27:433</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>East_River:434</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:15-May:2017-10-27:434</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16930,12 +16930,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>East_River:435</t>
+          <t>F1:East_River:Pumphouse_Floodplain:NA:1:15 cm +:2017-10-27:435</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16982,12 +16982,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>East_River:436</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:0-5:2017-10-27:436</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -17034,12 +17034,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>East_River:437</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:15-May:2017-10-27:437</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -17086,12 +17086,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>East_River:438</t>
+          <t>F2:East_River:Pumphouse_Floodplain:NA:2:15 cm +:2017-10-27:438</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -17138,12 +17138,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>East_River:439</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:0-5:2017-10-27:439</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -17190,12 +17190,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>East_River:440</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15-May:2017-10-27:440</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -17242,12 +17242,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>East_River:441</t>
+          <t>F3:East_River:Pumphouse_Floodplain:NA:3:15 cm +:2017-10-27:441</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -17294,12 +17294,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>East_River:442</t>
+          <t>TS:East_River:Pumphouse_Toeslope:NA:1:0-5:2017-10-27:442</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -17346,12 +17346,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>East_River:443</t>
+          <t>TS:East_River:Pumphouse_Toeslope:NA:1:15-May:2017-10-27:443</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>East_River:444</t>
+          <t>TS:East_River:Pumphouse_Toeslope:NA:1:15 cm +:2017-10-27:444</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Location:Lab_ID_LBNL</t>
+          <t>Plot:Location:Field_Site:Topographic_Position:Replicate:depth:date:Lab_ID_LBNL</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
